--- a/inputs/区间里程.xlsx
+++ b/inputs/区间里程.xlsx
@@ -4,12 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11480"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>station</t>
   </si>
@@ -37,36 +35,6 @@
     <t>mileage</t>
   </si>
   <si>
-    <t>beijingnan</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>langfang</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>tianjinnan</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>cangzhouxi</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>dezhoudong</t>
-  </si>
-  <si>
-    <t>327</t>
-  </si>
-  <si>
     <t>jinanxi</t>
   </si>
   <si>
@@ -101,78 +69,6 @@
   </si>
   <si>
     <t>688</t>
-  </si>
-  <si>
-    <t>suzhoudong</t>
-  </si>
-  <si>
-    <t>767</t>
-  </si>
-  <si>
-    <t>bengbunan</t>
-  </si>
-  <si>
-    <t>844</t>
-  </si>
-  <si>
-    <t>dingyuan</t>
-  </si>
-  <si>
-    <t>897</t>
-  </si>
-  <si>
-    <t>chuzhou</t>
-  </si>
-  <si>
-    <t>959</t>
-  </si>
-  <si>
-    <t>nanjingnan</t>
-  </si>
-  <si>
-    <t>1018</t>
-  </si>
-  <si>
-    <t>zhenjiangnan</t>
-  </si>
-  <si>
-    <t>1087</t>
-  </si>
-  <si>
-    <t>danyangbei</t>
-  </si>
-  <si>
-    <t>1112</t>
-  </si>
-  <si>
-    <t>changzhoubei</t>
-  </si>
-  <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>wuxidong</t>
-  </si>
-  <si>
-    <t>1201</t>
-  </si>
-  <si>
-    <t>suzhoubei</t>
-  </si>
-  <si>
-    <t>1227</t>
-  </si>
-  <si>
-    <t>kunshannan</t>
-  </si>
-  <si>
-    <t>1259</t>
-  </si>
-  <si>
-    <t>shanghaihongqiao</t>
-  </si>
-  <si>
-    <t>1302</t>
   </si>
 </sst>
 </file>
@@ -1114,10 +1010,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="10.1272727272727" customWidth="1"/>
+    <col min="1" max="1" width="35.5090909090909" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1184,186 +1080,9 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" ht="15" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" ht="15" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" ht="15" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" ht="15" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" ht="15" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" ht="15" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" ht="15" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" ht="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" ht="15" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" ht="15" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" ht="15" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="1"/>
-    </row>
-    <row r="19" ht="15" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="1"/>
-    </row>
-    <row r="20" ht="15" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="1"/>
-    </row>
-    <row r="21" ht="15" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" ht="15" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" ht="15" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" ht="15" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>